--- a/2. Báo cáo - giấy tờ/3. Sản xuất/Xuất nhập kho 2025/Nhập kho/Tháng 11/NKSX_LO4_349TB_TG102LE4G-56_151125.xlsx
+++ b/2. Báo cáo - giấy tờ/3. Sản xuất/Xuất nhập kho 2025/Nhập kho/Tháng 11/NKSX_LO4_349TB_TG102LE4G-56_151125.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\VNET\2. Báo cáo - giấy tờ\3. Sản xuất\Xuất nhập kho 2025\Nhập kho\Tháng 11\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\VNET\2. Báo cáo - giấy tờ\3. Sản xuất\Xuất Nhập Kho 2025\Nhập kho\Tháng 11\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2EAC574-78AE-4341-984D-78CA7FFFD06B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B3952BF7-35AC-469A-999B-F9DEB9FBF2D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="PhieuXuatKho" sheetId="10" r:id="rId1"/>
@@ -466,9 +466,6 @@
     <t>005694061498635</t>
   </si>
   <si>
-    <t>005194061496654</t>
-  </si>
-  <si>
     <t>005694061489667</t>
   </si>
   <si>
@@ -1184,6 +1181,9 @@
   </si>
   <si>
     <t>Địa chỉ: A46 TT19 Nguyễn Khuyến, P. Văn Quán, Q. Hà Đông, TP. Hà Nội</t>
+  </si>
+  <si>
+    <t>005694061496654</t>
   </si>
 </sst>
 </file>
@@ -2031,7 +2031,7 @@
       <c r="B2" s="4"/>
       <c r="C2" s="19"/>
       <c r="D2" s="63" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="E2" s="63"/>
       <c r="F2" s="63"/>
@@ -2386,16 +2386,16 @@
         <v>136</v>
       </c>
       <c r="E2" s="56" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="F2" s="56" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="G2" s="56" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="H2" s="56" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.2">
@@ -2412,16 +2412,16 @@
         <v>137</v>
       </c>
       <c r="E3" s="56" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="F3" s="56" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="G3" s="56" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="H3" s="56" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.2">
@@ -2438,16 +2438,16 @@
         <v>138</v>
       </c>
       <c r="E4" s="56" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="F4" s="56" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="G4" s="56" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="H4" s="56" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.2">
@@ -2464,16 +2464,16 @@
         <v>139</v>
       </c>
       <c r="E5" s="56" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="F5" s="56" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="G5" s="56" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="H5" s="56" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.2">
@@ -2490,16 +2490,16 @@
         <v>140</v>
       </c>
       <c r="E6" s="56" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F6" s="56" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="G6" s="56" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="H6" s="56" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.2">
@@ -2516,16 +2516,16 @@
         <v>141</v>
       </c>
       <c r="E7" s="56" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F7" s="56" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="G7" s="56" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="H7" s="56" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.2">
@@ -2542,16 +2542,16 @@
         <v>142</v>
       </c>
       <c r="E8" s="56" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="F8" s="56" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="G8" s="56" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="H8" s="56" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="J8" s="40"/>
     </row>
@@ -2569,16 +2569,16 @@
         <v>143</v>
       </c>
       <c r="E9" s="56" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="F9" s="56" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="G9" s="56" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="H9" s="56" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.2">
@@ -2595,16 +2595,16 @@
         <v>144</v>
       </c>
       <c r="E10" s="56" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="F10" s="56" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="G10" s="56" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H10" s="56" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.2">
@@ -2621,16 +2621,16 @@
         <v>145</v>
       </c>
       <c r="E11" s="56" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="F11" s="56" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="G11" s="56" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="H11" s="56" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.2">
@@ -2644,19 +2644,19 @@
         <v>96</v>
       </c>
       <c r="D12" s="56" t="s">
-        <v>146</v>
+        <v>385</v>
       </c>
       <c r="E12" s="56" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="F12" s="56" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="G12" s="56" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="H12" s="56" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.2">
@@ -2670,19 +2670,19 @@
         <v>97</v>
       </c>
       <c r="D13" s="56" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="E13" s="56" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="F13" s="56" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="G13" s="56" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="H13" s="56" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.2">
@@ -2696,19 +2696,19 @@
         <v>98</v>
       </c>
       <c r="D14" s="56" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E14" s="56" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="F14" s="56" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="G14" s="56" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="H14" s="56" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.2">
@@ -2722,19 +2722,19 @@
         <v>99</v>
       </c>
       <c r="D15" s="56" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="E15" s="56" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="F15" s="56" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="G15" s="56" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="H15" s="56" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.2">
@@ -2748,19 +2748,19 @@
         <v>100</v>
       </c>
       <c r="D16" s="56" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="E16" s="56" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="F16" s="56" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="G16" s="56" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="H16" s="56" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.2">
@@ -2774,19 +2774,19 @@
         <v>101</v>
       </c>
       <c r="D17" s="56" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="E17" s="56" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="F17" s="56" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="G17" s="56" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="H17" s="56" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.2">
@@ -2800,19 +2800,19 @@
         <v>102</v>
       </c>
       <c r="D18" s="56" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="E18" s="56" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="F18" s="56" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="G18" s="56" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="H18" s="56" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.2">
@@ -2826,19 +2826,19 @@
         <v>103</v>
       </c>
       <c r="D19" s="56" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="E19" s="56" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="F19" s="56" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="G19" s="56" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="H19" s="56" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.2">
@@ -2852,19 +2852,19 @@
         <v>104</v>
       </c>
       <c r="D20" s="56" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="E20" s="56" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="F20" s="56" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="G20" s="56" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="H20" s="56" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.2">
@@ -2878,19 +2878,19 @@
         <v>105</v>
       </c>
       <c r="D21" s="56" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E21" s="56" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="F21" s="56" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="G21" s="56" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="H21" s="56" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.2">
@@ -2904,19 +2904,19 @@
         <v>106</v>
       </c>
       <c r="D22" s="56" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="E22" s="56" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="F22" s="56" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="G22" s="56" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="H22" s="56" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.2">
@@ -2930,19 +2930,19 @@
         <v>107</v>
       </c>
       <c r="D23" s="56" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="E23" s="56" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F23" s="56" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="G23" s="56" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="H23" s="56" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.2">
@@ -2956,19 +2956,19 @@
         <v>108</v>
       </c>
       <c r="D24" s="56" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E24" s="56" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="F24" s="56" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="G24" s="56" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="H24" s="56" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.2">
@@ -2982,19 +2982,19 @@
         <v>109</v>
       </c>
       <c r="D25" s="56" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="E25" s="56" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="F25" s="56" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="G25" s="56" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="H25" s="56" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.2">
@@ -3008,19 +3008,19 @@
         <v>110</v>
       </c>
       <c r="D26" s="56" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E26" s="56" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="F26" s="56" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="G26" s="56" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="H26" s="56" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.2">
@@ -3034,19 +3034,19 @@
         <v>111</v>
       </c>
       <c r="D27" s="56" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="E27" s="56" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="F27" s="56" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="G27" s="56" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="H27" s="56" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.2">
@@ -3060,19 +3060,19 @@
         <v>112</v>
       </c>
       <c r="D28" s="56" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="E28" s="56" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="F28" s="56" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="G28" s="56" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="H28" s="56" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.2">
@@ -3086,19 +3086,19 @@
         <v>113</v>
       </c>
       <c r="D29" s="56" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="E29" s="56" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="F29" s="56" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="G29" s="56" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="H29" s="56" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.2">
@@ -3112,19 +3112,19 @@
         <v>114</v>
       </c>
       <c r="D30" s="56" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="E30" s="56" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="F30" s="56" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="G30" s="56" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="H30" s="56" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.2">
@@ -3138,19 +3138,19 @@
         <v>115</v>
       </c>
       <c r="D31" s="56" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="E31" s="56" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="F31" s="56" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="G31" s="56" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="H31" s="56" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.2">
@@ -3164,19 +3164,19 @@
         <v>116</v>
       </c>
       <c r="D32" s="56" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="E32" s="56" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="F32" s="56" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="G32" s="56" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="H32" s="56" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.2">
@@ -3190,19 +3190,19 @@
         <v>117</v>
       </c>
       <c r="D33" s="56" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="E33" s="56" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="F33" s="56" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="G33" s="56" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="H33" s="56" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.2">
@@ -3216,19 +3216,19 @@
         <v>118</v>
       </c>
       <c r="D34" s="56" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="E34" s="56" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="F34" s="56" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="G34" s="56" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="H34" s="56" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.2">
@@ -3242,19 +3242,19 @@
         <v>119</v>
       </c>
       <c r="D35" s="56" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E35" s="56" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="F35" s="56" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="G35" s="56" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="H35" s="56" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.2">
@@ -3268,19 +3268,19 @@
         <v>120</v>
       </c>
       <c r="D36" s="56" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="E36" s="56" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="F36" s="56" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="G36" s="56" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="H36" s="56" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.2">
@@ -3294,19 +3294,19 @@
         <v>121</v>
       </c>
       <c r="D37" s="56" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="E37" s="56" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="F37" s="56" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="G37" s="56" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="H37" s="56" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.2">
@@ -3320,19 +3320,19 @@
         <v>122</v>
       </c>
       <c r="D38" s="56" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="E38" s="56" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="F38" s="56" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="G38" s="56" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="H38" s="56" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.2">
@@ -3346,19 +3346,19 @@
         <v>123</v>
       </c>
       <c r="D39" s="56" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E39" s="56" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="F39" s="56" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="G39" s="56" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="H39" s="56" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.2">
@@ -3372,19 +3372,19 @@
         <v>124</v>
       </c>
       <c r="D40" s="56" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="E40" s="56" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="F40" s="56" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="G40" s="56" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="H40" s="56" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.2">
@@ -3398,19 +3398,19 @@
         <v>125</v>
       </c>
       <c r="D41" s="56" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="E41" s="56" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="F41" s="56" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="G41" s="56" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="H41" s="56" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.2">
@@ -3424,19 +3424,19 @@
         <v>126</v>
       </c>
       <c r="D42" s="56" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="E42" s="56" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="F42" s="56" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="G42" s="56" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="H42" s="56" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.2">
@@ -3450,19 +3450,19 @@
         <v>127</v>
       </c>
       <c r="D43" s="56" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="E43" s="56" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="F43" s="56" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="G43" s="56" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="H43" s="56" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.2">
@@ -3476,19 +3476,19 @@
         <v>128</v>
       </c>
       <c r="D44" s="56" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="E44" s="56" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="F44" s="56" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="G44" s="56" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="H44" s="56" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.2">
@@ -3502,19 +3502,19 @@
         <v>129</v>
       </c>
       <c r="D45" s="56" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="E45" s="56" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="F45" s="56" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="G45" s="56" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="H45" s="56" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.2">
@@ -3528,19 +3528,19 @@
         <v>130</v>
       </c>
       <c r="D46" s="56" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="E46" s="56" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="F46" s="56" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="G46" s="56" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="H46" s="56" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.2">
@@ -3554,19 +3554,19 @@
         <v>131</v>
       </c>
       <c r="D47" s="56" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="E47" s="56" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="F47" s="56" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="G47" s="56" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="H47" s="56" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.2">
@@ -3580,19 +3580,19 @@
         <v>132</v>
       </c>
       <c r="D48" s="56" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="E48" s="56" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="F48" s="56" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="G48" s="56" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="H48" s="56" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.2">
@@ -3606,19 +3606,19 @@
         <v>133</v>
       </c>
       <c r="D49" s="56" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E49" s="56" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="F49" s="56" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="G49" s="56" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="H49" s="56" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.2">
@@ -3632,19 +3632,19 @@
         <v>134</v>
       </c>
       <c r="D50" s="56" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="E50" s="56" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="F50" s="56" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="G50" s="56" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="H50" s="56" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.2">
@@ -3658,16 +3658,16 @@
         <v>135</v>
       </c>
       <c r="D51" s="56" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="E51" s="56" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="F51" s="56" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="G51" s="56" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="H51" s="56"/>
     </row>
